--- a/data/trans_orig/P17G-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P17G-Habitat-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>909</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117255</t>
+          <t>118144</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125983</t>
+          <t>126003</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199270</t>
+          <t>199114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210325</t>
+          <t>210368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>321208</t>
+          <t>320461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>334588</t>
+          <t>334500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27752</t>
+          <t>29256</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>24548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164209</t>
+          <t>164077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180739</t>
+          <t>180860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275901</t>
+          <t>275976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294088</t>
+          <t>294549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>447555</t>
+          <t>446454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471450</t>
+          <t>471618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27383</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21187</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116533</t>
+          <t>115705</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>133296</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173197</t>
+          <t>172028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189950</t>
+          <t>188868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>294752</t>
+          <t>295843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>317891</t>
+          <t>318959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,82 +2907,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>6045</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2181</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>12253</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>20700</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>6045</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>12693</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>13112</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>7504</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>21254</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11558</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>29467</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>160136</t>
+          <t>160554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179159</t>
+          <t>178362</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>299728</t>
+          <t>298713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>316304</t>
+          <t>315768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>465022</t>
+          <t>464248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>490788</t>
+          <t>490968</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36974</t>
+          <t>35903</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20450</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>44864</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>75896</t>
+          <t>75188</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27078</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>55829</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>576484</t>
+          <t>576662</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>607664</t>
+          <t>607753</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>964140</t>
+          <t>965119</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>997163</t>
+          <t>997968</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1552659</t>
+          <t>1556823</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1598206</t>
+          <t>1599828</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160165</t>
+          <t>160073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171439</t>
+          <t>171349</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224619</t>
+          <t>224326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231988</t>
+          <t>231994</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389349</t>
+          <t>388573</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402692</t>
+          <t>402197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30755</t>
+          <t>31691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>208619</t>
+          <t>207923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226600</t>
+          <t>226012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>324366</t>
+          <t>324640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>340551</t>
+          <t>340957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>539080</t>
+          <t>540316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>563217</t>
+          <t>563712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149938</t>
+          <t>151391</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166552</t>
+          <t>167180</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214322</t>
+          <t>215775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226555</t>
+          <t>227410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>370191</t>
+          <t>372170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>391019</t>
+          <t>391740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>21215</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>25717</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159760</t>
+          <t>160539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>176412</t>
+          <t>176134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>293176</t>
+          <t>293670</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>312223</t>
+          <t>312312</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>460313</t>
+          <t>459871</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>484619</t>
+          <t>483672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>15763</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>29615</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>26954</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52313</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15574</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>35727</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>66592</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>700016</t>
+          <t>700099</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>730239</t>
+          <t>731373</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1074049</t>
+          <t>1075045</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1103455</t>
+          <t>1103089</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1784283</t>
+          <t>1784250</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1825624</t>
+          <t>1826164</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174030</t>
+          <t>174216</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185311</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220670</t>
+          <t>220675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236958</t>
+          <t>236972</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>399941</t>
+          <t>400688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>419420</t>
+          <t>419431</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18962</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41256</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226576</t>
+          <t>225954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>246164</t>
+          <t>247189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>325211</t>
+          <t>324946</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339479</t>
+          <t>339899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>556273</t>
+          <t>556989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>581909</t>
+          <t>583020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154827</t>
+          <t>153767</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168882</t>
+          <t>168601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223514</t>
+          <t>222040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239008</t>
+          <t>238678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>383801</t>
+          <t>384991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>404048</t>
+          <t>404707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26277</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27261</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50715</t>
+          <t>50160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>175924</t>
+          <t>176722</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>197785</t>
+          <t>198243</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>263123</t>
+          <t>262465</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>285460</t>
+          <t>285325</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>448363</t>
+          <t>448723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>478289</t>
+          <t>477929</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>25124</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>31387</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50714</t>
+          <t>48739</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60295</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33883</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>62586</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>74480</t>
+          <t>72564</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>114704</t>
+          <t>114013</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>753571</t>
+          <t>750704</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>786816</t>
+          <t>786560</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1052613</t>
+          <t>1054730</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1087723</t>
+          <t>1088154</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1815051</t>
+          <t>1815344</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1864231</t>
+          <t>1864046</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -11812,12 +11812,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -11847,12 +11847,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>110846</t>
+          <t>118311</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106820</t>
+          <t>112539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112651</t>
+          <t>120294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>162778</t>
+          <t>174266</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158270</t>
+          <t>169233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165415</t>
+          <t>176828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>273624</t>
+          <t>292577</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267774</t>
+          <t>286789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>276918</t>
+          <t>296214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>168083</t>
+          <t>179816</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>168083</t>
+          <t>179816</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168083</t>
+          <t>179816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>703</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>703</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,22 +12519,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18649</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>32166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19967</t>
+          <t>21881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>21649</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>32620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>160750</t>
+          <t>177393</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148608</t>
+          <t>165571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170082</t>
+          <t>187015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>197530</t>
+          <t>224960</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189715</t>
+          <t>216488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203443</t>
+          <t>231023</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>358281</t>
+          <t>402353</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344322</t>
+          <t>387698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>369271</t>
+          <t>414235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>184235</t>
+          <t>204293</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>184235</t>
+          <t>204293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>184235</t>
+          <t>204293</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>245527</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>245527</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>245527</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>401280</t>
+          <t>449820</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>401280</t>
+          <t>449820</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>401280</t>
+          <t>449820</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -13176,12 +13176,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35757</t>
+          <t>37628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14878</t>
+          <t>17518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>114492</t>
+          <t>125632</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102607</t>
+          <t>112224</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121800</t>
+          <t>134174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>128466</t>
+          <t>156871</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120022</t>
+          <t>147988</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134149</t>
+          <t>163770</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>242958</t>
+          <t>282502</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>229182</t>
+          <t>269105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253332</t>
+          <t>293804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>148782</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>148782</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148782</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>282447</t>
+          <t>326086</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>282447</t>
+          <t>326086</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>282447</t>
+          <t>326086</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>675</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -13745,12 +13745,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>675</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -13780,12 +13780,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>38616</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>32885</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46492</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17959</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23971</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15716</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37110</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>189099</t>
+          <t>196665</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>180044</t>
+          <t>186576</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>196752</t>
+          <t>204143</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>320553</t>
+          <t>276740</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>305024</t>
+          <t>263562</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339635</t>
+          <t>287205</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>509652</t>
+          <t>473406</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>491777</t>
+          <t>458085</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>531328</t>
+          <t>487492</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>210347</t>
+          <t>219239</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>210347</t>
+          <t>219239</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>210347</t>
+          <t>219239</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>362652</t>
+          <t>321523</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>362652</t>
+          <t>321523</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>362652</t>
+          <t>321523</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>572999</t>
+          <t>540763</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>572999</t>
+          <t>540763</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>572999</t>
+          <t>540763</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>12901</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22753</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>32671</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>22823</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49384</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>45385</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>38724</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57811</t>
+          <t>63047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>78055</t>
+          <t>84362</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61205</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>96893</t>
+          <t>103532</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33871</t>
+          <t>35686</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24750</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45284</t>
+          <t>46563</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,27 +14791,27 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>65006</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>46960</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76626</t>
+          <t>80492</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>575187</t>
+          <t>618001</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>557031</t>
+          <t>597741</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>591366</t>
+          <t>634600</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>809327</t>
+          <t>832836</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>792039</t>
+          <t>817036</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>831417</t>
+          <t>848645</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1384514</t>
+          <t>1450837</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1358544</t>
+          <t>1426064</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1410118</t>
+          <t>1471984</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
